--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/1341-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/1341-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{194A2BCF-0D83-4BAA-84AF-EEF6DE8AF58F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BFF5079D-D0FC-4469-86C5-0AC3914C6CB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{78DC7E45-515E-4849-9871-5155EAC61172}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{F313321C-F1A1-454B-B415-3E07ADF0FBD7}"/>
   </bookViews>
   <sheets>
     <sheet name="1341-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1484,21 +1484,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D8053C4-6F26-4C6A-9579-99DCEA495C17}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{607D0F04-88AA-4197-A789-89C2C03D3795}">
   <dimension ref="A1:R30"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="9.109375" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="11.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1526,7 +1526,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1556,7 +1556,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1602,7 +1602,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1652,7 +1652,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1706,7 +1706,7 @@
         <v>6.96</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1762,7 +1762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1818,7 +1818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>25</v>
       </c>
@@ -1874,7 +1874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>25</v>
       </c>
@@ -1930,7 +1930,7 @@
         <v>6.96</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="39">
         <v>2024</v>
       </c>
@@ -1984,7 +1984,7 @@
         <v>6.17</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>25</v>
       </c>
@@ -2040,7 +2040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
         <v>25</v>
       </c>
@@ -2096,7 +2096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
         <v>25</v>
       </c>
@@ -2152,7 +2152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
         <v>25</v>
       </c>
@@ -2208,7 +2208,7 @@
         <v>6.17</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>25</v>
       </c>
@@ -2264,7 +2264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>25</v>
       </c>
@@ -2320,7 +2320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="37">
         <v>2023</v>
       </c>
@@ -2374,7 +2374,7 @@
         <v>4.18</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>25</v>
       </c>
@@ -2430,7 +2430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -2486,7 +2486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>25</v>
       </c>
@@ -2542,7 +2542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>25</v>
       </c>
@@ -2598,7 +2598,7 @@
         <v>4.18</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="39">
         <v>2022</v>
       </c>
@@ -2652,7 +2652,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>25</v>
       </c>
@@ -2708,7 +2708,7 @@
         <v>4.37</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>25</v>
       </c>
@@ -2764,7 +2764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="s">
         <v>25</v>
       </c>
@@ -2820,7 +2820,7 @@
         <v>8.1199999999999992</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="37">
         <v>2021</v>
       </c>
@@ -2874,7 +2874,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="39">
         <v>2020</v>
       </c>
@@ -2928,7 +2928,7 @@
         <v>7.35</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="37">
         <v>2019</v>
       </c>
@@ -2982,7 +2982,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="39">
         <v>2018</v>
       </c>
@@ -3036,7 +3036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="37" t="s">
         <v>47</v>
       </c>
